--- a/test-results/需求.xlsx
+++ b/test-results/需求.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>品牌</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>单价</t>
+  </si>
+  <si>
+    <t>物料编码</t>
   </si>
   <si>
     <t>合作供货商</t>
@@ -458,18 +461,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -499,44 +502,47 @@
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/test-results/需求.xlsx
+++ b/test-results/需求.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>品牌</t>
   </si>
@@ -37,6 +37,9 @@
     <t>物料编码</t>
   </si>
   <si>
+    <t>需求公司</t>
+  </si>
+  <si>
     <t>合作供货商</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t>个</t>
+  </si>
+  <si>
+    <t>武汉吉利汽车部件有限公司</t>
   </si>
   <si>
     <t>待查品牌</t>
@@ -461,18 +467,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="55" customWidth="1"/>
+    <col min="7" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -506,43 +512,55 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/test-results/需求.xlsx
+++ b/test-results/需求.xlsx
@@ -532,9 +532,6 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
       <c r="I2" t="s">
         <v>17</v>
       </c>
